--- a/ЛР1_Спрос_и_границы_рынка/Excel/XLT_A_только_YW_TableMind.xlsx
+++ b/ЛР1_Спрос_и_границы_рынка/Excel/XLT_A_только_YW_TableMind.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\ЛР1_Спрос_и_границы_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР1_Спрос_и_границы_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7160F80-DF49-42D8-818F-ECB9A1F666C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76AA710-0D7E-4A94-9C8A-49C726149A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Панель" sheetId="1" r:id="rId1"/>
@@ -42,12 +42,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="212">
   <si>
     <t>Панель оценки тренда, сезонности и циклов спроса</t>
-  </si>
-  <si>
-    <t>Файл предназначен для анализа интереса аудитории на основе выгрузок из Google Trends и Яндекс Вордстат. Заполните лист «Ввод_данных», после чего показатели на этой панели обновятся автоматически.</t>
   </si>
   <si>
     <t>Блок</t>
@@ -57,9 +54,6 @@
   </si>
   <si>
     <t>Значение</t>
-  </si>
-  <si>
-    <t>Как использовать</t>
   </si>
   <si>
     <t>Данные</t>
@@ -122,22 +116,13 @@
     <t>значение выше 1 означает спрос выше трендово-сезонного уровня</t>
   </si>
   <si>
-    <t>Итоговая формулировка для отчета</t>
-  </si>
-  <si>
     <t>Ввод данных из Google Trends и Яндекс Вордстат</t>
-  </si>
-  <si>
-    <t>Заполните строки по месяцам. Google Trends вводится как индекс 0–100. Яндекс Вордстат вводится как абсолютное число запросов по выбранному семантическому кластеру. В демонстрационном примере приведены условные данные для бизнеса на основе компетенции «маркетинг».</t>
   </si>
   <si>
     <t>Период</t>
   </si>
   <si>
     <t>Кластер запросов</t>
-  </si>
-  <si>
-    <t>Google Trends, 0–100</t>
   </si>
   <si>
     <t>Яндекс Вордстат, запросов</t>
@@ -152,9 +137,6 @@
     <t>Расчет тренда, сезонности и циклических отклонений</t>
   </si>
   <si>
-    <t>Расчет построен по мультипликативной логике: наблюдаемый интерес = тренд × сезонность × циклическое отклонение × случайные колебания. Для практической оценки используются скользящее среднее, сезонные индексы и коэффициент отклонения от трендово-сезонного уровня.</t>
-  </si>
-  <si>
     <t>Месяц №</t>
   </si>
   <si>
@@ -167,13 +149,7 @@
     <t>Вордстат</t>
   </si>
   <si>
-    <t>Вордстат норм. 0–100</t>
-  </si>
-  <si>
     <t>Сводный индекс</t>
-  </si>
-  <si>
-    <t>Тренд: скользящее среднее 12 мес.</t>
   </si>
   <si>
     <t>Y/T</t>
@@ -330,9 +306,6 @@
   </si>
   <si>
     <t>Оценка циклических отклонений и фаз спроса</t>
-  </si>
-  <si>
-    <t>Важно: данные Google Trends и Яндекс Вордстат не измеряют макроэкономический деловой цикл напрямую. В таблице оценивается поисковый цикл спроса: периоды, когда интерес находится выше или ниже трендово-сезонного уровня.</t>
   </si>
   <si>
     <t>Последний период</t>
@@ -612,6 +585,102 @@
   </si>
   <si>
     <t>вкладка «Динамика», все устройства; значения запросов кластера суммированы</t>
+  </si>
+  <si>
+    <t>Производится анализ интереса аудитории на основе выгрузок из Google Trends и Яндекс Вордстат.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Trends вводится как индекс 0-100. 
+Яндекс Вордстат вводится как абсолютное число запросов по выбранному семантическому кластеру. </t>
+  </si>
+  <si>
+    <t>Расчет построен по мультипликативной логике. 
+Наблюдаемый интерес = тренд × сезонность × циклическое отклонение × случайные колебания. 
+Для практической оценки используются скользящее среднее, сезонные индексы и коэффициент отклонения от трендово-сезонного уровня.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В таблице оценивается поисковый цикл спроса, то есть периоды, когда интерес находится выше или ниже трендово-сезонного уровня. </t>
+  </si>
+  <si>
+    <t>Использование</t>
+  </si>
+  <si>
+    <t>Вывод:</t>
+  </si>
+  <si>
+    <t>Google Trends, 0-100</t>
+  </si>
+  <si>
+    <t>Вордстат норм. 0-100</t>
+  </si>
+  <si>
+    <t>Скользящее среднее 12 мес. (тренд)</t>
+  </si>
+  <si>
+    <t>Вордстат в нижней четверти значений ряда; начало ряда</t>
+  </si>
+  <si>
+    <t>Вордстат выше медианы ряда, рост к предыдущему месяцу на 37 %</t>
+  </si>
+  <si>
+    <t>Вордстат в верхней четверти значений ряда</t>
+  </si>
+  <si>
+    <t>Вордстат в нижней четверти значений ряда, снижение к предыдущему месяцу на 29 %</t>
+  </si>
+  <si>
+    <t>Вордстат ниже медианы ряда</t>
+  </si>
+  <si>
+    <t>Вордстат выше медианы ряда</t>
+  </si>
+  <si>
+    <t>Вордстат в нижней четверти значений ряда</t>
+  </si>
+  <si>
+    <t>Вордстат в нижней четверти значений ряда, снижение к предыдущему месяцу на 35 %</t>
+  </si>
+  <si>
+    <t>Вордстат ниже медианы ряда, снижение к предыдущему месяцу на 27 %</t>
+  </si>
+  <si>
+    <t>Вордстат в нижней четверти значений ряда, снижение к предыдущему месяцу на 33 %</t>
+  </si>
+  <si>
+    <t>Вордстат в верхней четверти значений ряда, рост к предыдущему месяцу на 63 %</t>
+  </si>
+  <si>
+    <t>Вордстат максимум ряда, рост к предыдущему месяцу на 38 %</t>
+  </si>
+  <si>
+    <t>Вордстат выше медианы ряда, снижение к предыдущему месяцу на 32 %</t>
+  </si>
+  <si>
+    <t>Вордстат в верхней четверти значений ряда, рост к предыдущему месяцу на 35 %</t>
+  </si>
+  <si>
+    <t>Вордстат в нижней четверти значений ряда, снижение к предыдущему месяцу на 50 %</t>
+  </si>
+  <si>
+    <t>Вордстат выше медианы ряда, рост к предыдущему месяцу на 50 %</t>
+  </si>
+  <si>
+    <t>Вордстат в нижней четверти значений ряда, снижение к предыдущему месяцу на 52 %</t>
+  </si>
+  <si>
+    <t>Вордстат минимум ряда</t>
+  </si>
+  <si>
+    <t>Вордстат в нижней четверти значений ряда, рост к предыдущему месяцу на 51 %; конец ряда, выгрузка от 02.10.2026</t>
+  </si>
+  <si>
+    <t>https://otexts.com/fpp3/moving-averages.html</t>
+  </si>
+  <si>
+    <t>https://otexts.com/fpp3/classical-decomposition.html</t>
+  </si>
+  <si>
+    <t>https://otexts.com/fpp3/tspatterns.html</t>
   </si>
 </sst>
 </file>
@@ -1939,7 +2008,7 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Период"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Кластер запросов"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Google Trends, 0–100"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Google Trends, 0-100"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Яндекс Вордстат, запросов"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Регион / рынок"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Комментарий"/>
@@ -1956,9 +2025,9 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Месяц"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Google Trends"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Вордстат"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Вордстат норм. 0–100"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Вордстат норм. 0-100"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Сводный индекс"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Тренд: скользящее среднее 12 мес."/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Скользящее среднее 12 мес. (тренд)"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Y/T"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Сезонно очищенный индекс"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Циклический коэффициент"/>
@@ -2273,7 +2342,7 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="12" t="s">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2331,16 +2400,16 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>185</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -2367,17 +2436,17 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3">
         <f>Оценка_тренда!B4</f>
         <v>60</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -2404,17 +2473,17 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="str">
         <f>Оценка_тренда!B10</f>
         <v>стабильный тренд</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -2441,17 +2510,17 @@
     </row>
     <row r="8" spans="1:26" ht="26.25">
       <c r="A8" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" s="4">
         <f>Оценка_тренда!B8</f>
         <v>0.12029368312665069</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -2478,17 +2547,17 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>Сезонность!B22</f>
         <v>выраженная сезонность</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2515,17 +2584,17 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="str">
         <f>Сезонность!B23</f>
         <v>декабрь</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -2552,17 +2621,17 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="str">
         <f>Сезонность!B24</f>
         <v>август</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -2589,17 +2658,17 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="str">
         <f>Деловые_циклы!B7</f>
         <v>ниже тренда</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -2626,17 +2695,17 @@
     </row>
     <row r="13" spans="1:26" ht="26.25">
       <c r="A13" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="5">
         <f>Деловые_циклы!B6</f>
         <v>0.78665764018689743</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -2719,7 +2788,7 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="13" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2749,8 +2818,8 @@
     </row>
     <row r="17" spans="1:26">
       <c r="A17" s="14" t="str">
-        <f>Оценка_тренда!B11&amp;" Сезонность: "&amp;Сезонность!B22&amp;"; максимум интереса — "&amp;Сезонность!B23&amp;", минимум — "&amp;Сезонность!B24&amp;". Текущая фаза спроса: "&amp;Деловые_циклы!B7&amp;"."</f>
-        <v>Интерес аудитории относительно стабилен; целесообразно изучить структуру спроса, конкурентов и целевые сегменты. Сезонность: выраженная сезонность; максимум интереса — декабрь, минимум — август. Текущая фаза спроса: ниже тренда.</v>
+        <f>Оценка_тренда!B11&amp;" Для ряда характерна "&amp;Сезонность!B22&amp;", максимум интереса приходится на "&amp;Сезонность!B23&amp;", минимум на "&amp;Сезонность!B24&amp;". Текущая фаза спроса - "&amp;Деловые_циклы!B7&amp;"."</f>
+        <v>Интерес аудитории относительно стабилен; целесообразно изучить структуру спроса, конкурентов и целевые сегменты. Для ряда характерна выраженная сезонность, максимум интереса приходится на декабрь, минимум на август. Текущая фаза спроса - ниже тренда.</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -5129,7 +5198,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5159,7 +5228,7 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="12" t="s">
-        <v>28</v>
+        <v>182</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -5215,24 +5284,24 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="26.25">
+    <row r="4" spans="1:26">
       <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -5255,21 +5324,23 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" ht="26.25">
       <c r="A5" s="6">
         <v>44470</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7">
         <v>1683</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>190</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -5291,21 +5362,23 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:26" ht="26.25">
       <c r="A6" s="6">
         <v>44501</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7">
         <v>2298</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -5332,16 +5405,18 @@
         <v>44531</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7">
         <v>2523</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -5363,21 +5438,23 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:26" ht="26.25">
       <c r="A8" s="6">
         <v>44562</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7">
         <v>1793</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -5404,16 +5481,18 @@
         <v>44593</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7">
         <v>1909</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -5440,16 +5519,18 @@
         <v>44621</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7">
         <v>2207</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -5476,16 +5557,18 @@
         <v>44652</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7">
         <v>2055</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -5512,16 +5595,18 @@
         <v>44682</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7">
         <v>1948</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -5548,16 +5633,18 @@
         <v>44713</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7">
         <v>1806</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -5579,21 +5666,23 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:26" ht="26.25">
       <c r="A14" s="6">
         <v>44743</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7">
         <v>1175</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F14" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>197</v>
+      </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -5620,16 +5709,18 @@
         <v>44774</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7">
         <v>1313</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F15" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -5656,16 +5747,18 @@
         <v>44805</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7">
         <v>1627</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F16" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -5692,16 +5785,18 @@
         <v>44835</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7">
         <v>1868</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -5728,16 +5823,18 @@
         <v>44866</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7">
         <v>2316</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F18" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -5764,16 +5861,18 @@
         <v>44896</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7">
         <v>2704</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F19" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -5795,21 +5894,23 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:26" ht="26.25">
       <c r="A20" s="6">
         <v>44927</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7">
         <v>1979</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F20" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -5836,16 +5937,18 @@
         <v>44958</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7">
         <v>1815</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F21" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -5872,16 +5975,18 @@
         <v>44986</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7">
         <v>2218</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -5908,16 +6013,18 @@
         <v>45017</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7">
         <v>2146</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F23" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -5944,16 +6051,18 @@
         <v>45047</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7">
         <v>2267</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -5980,16 +6089,18 @@
         <v>45078</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7">
         <v>1932</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F25" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -6016,16 +6127,18 @@
         <v>45108</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7">
         <v>1795</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F26" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -6052,16 +6165,18 @@
         <v>45139</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7">
         <v>1936</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -6088,16 +6203,18 @@
         <v>45170</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7">
         <v>2438</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -6124,16 +6241,18 @@
         <v>45200</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7">
         <v>2726</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F29" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -6160,16 +6279,18 @@
         <v>45231</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7">
         <v>2727</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F30" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -6196,16 +6317,18 @@
         <v>45261</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7">
         <v>2621</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F31" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -6232,16 +6355,18 @@
         <v>45292</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7">
         <v>1978</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F32" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -6268,16 +6393,18 @@
         <v>45323</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7">
         <v>1950</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F33" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -6304,16 +6431,18 @@
         <v>45352</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7">
         <v>2248</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -6340,16 +6469,18 @@
         <v>45383</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7">
         <v>2221</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F35" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -6376,16 +6507,18 @@
         <v>45413</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7">
         <v>2379</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -6412,16 +6545,18 @@
         <v>45444</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7">
         <v>2085</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -6443,21 +6578,23 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" spans="1:26" ht="26.25">
       <c r="A38" s="6">
         <v>45474</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7">
         <v>1402</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>199</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -6484,16 +6621,18 @@
         <v>45505</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7">
         <v>1397</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F39" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -6520,16 +6659,18 @@
         <v>45536</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7">
         <v>1638</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F40" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -6551,21 +6692,23 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" spans="1:26" ht="26.25">
       <c r="A41" s="6">
         <v>45566</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7">
         <v>2670</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F41" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -6592,16 +6735,18 @@
         <v>45597</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7">
         <v>2610</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F42" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -6623,21 +6768,23 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26">
+    <row r="43" spans="1:26" ht="26.25">
       <c r="A43" s="6">
         <v>45627</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7">
         <v>3592</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F43" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -6659,21 +6806,23 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26">
+    <row r="44" spans="1:26" ht="26.25">
       <c r="A44" s="6">
         <v>45658</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7">
         <v>2441</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F44" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -6700,16 +6849,18 @@
         <v>45689</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7">
         <v>2515</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F45" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -6736,16 +6887,18 @@
         <v>45717</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7">
         <v>2430</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F46" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -6767,21 +6920,23 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26">
+    <row r="47" spans="1:26" ht="26.25">
       <c r="A47" s="6">
         <v>45748</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7">
         <v>3285</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F47" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -6808,16 +6963,18 @@
         <v>45778</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7">
         <v>2702</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F48" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -6844,16 +7001,18 @@
         <v>45809</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7">
         <v>3006</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F49" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -6875,21 +7034,23 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26">
+    <row r="50" spans="1:26" ht="26.25">
       <c r="A50" s="6">
         <v>45839</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="7">
         <v>1505</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F50" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -6916,16 +7077,18 @@
         <v>45870</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7">
         <v>1457</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F51" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -6947,21 +7110,23 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26">
+    <row r="52" spans="1:26" ht="26.25">
       <c r="A52" s="6">
         <v>45901</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7">
         <v>2190</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F52" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -6988,16 +7153,18 @@
         <v>45931</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7">
         <v>2600</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F53" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -7024,16 +7191,18 @@
         <v>45962</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7">
         <v>3283</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F54" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -7060,16 +7229,18 @@
         <v>45992</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7">
         <v>3403</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F55" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -7091,21 +7262,23 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" spans="1:26" ht="26.25">
       <c r="A56" s="6">
         <v>46023</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7">
         <v>1703</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F56" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -7132,16 +7305,18 @@
         <v>46054</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7">
         <v>1822</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F57" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -7168,16 +7343,18 @@
         <v>46082</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7">
         <v>2045</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F58" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -7204,16 +7381,18 @@
         <v>46113</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7">
         <v>2275</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F59" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -7240,16 +7419,18 @@
         <v>46143</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7">
         <v>2146</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F60" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -7276,16 +7457,18 @@
         <v>46174</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7">
         <v>2289</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F61" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -7307,21 +7490,23 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26">
+    <row r="62" spans="1:26" ht="26.25">
       <c r="A62" s="6">
         <v>46204</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7">
         <v>1099</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F62" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -7348,16 +7533,18 @@
         <v>46235</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7">
         <v>940</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F63" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>207</v>
+      </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -7379,21 +7566,23 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26">
+    <row r="64" spans="1:26" ht="39.4">
       <c r="A64" s="6">
         <v>46266</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7">
         <v>1419</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F64" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -8456,7 +8645,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8486,7 +8675,7 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="12" t="s">
-        <v>36</v>
+        <v>183</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -8544,46 +8733,46 @@
     </row>
     <row r="4" spans="1:26" ht="26.25">
       <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -8648,8 +8837,8 @@
         <v/>
       </c>
       <c r="M5" s="3" t="str">
-        <f t="shared" ref="M5:M36" si="4">IF(L5="","",IF(L5="ниже тренда","возможное ослабление интереса",IF(L5="выше тренда","возможная фаза повышенного интереса","без выраженного отклонения")))</f>
-        <v/>
+        <f>IF(G5="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N5" s="7">
         <f>IF(G5="","",COUNT($G$5:G5))</f>
@@ -8718,8 +8907,8 @@
         <v/>
       </c>
       <c r="M6" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G6="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N6" s="7">
         <f>IF(G6="","",COUNT($G$5:G6))</f>
@@ -8788,8 +8977,8 @@
         <v/>
       </c>
       <c r="M7" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G7="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N7" s="7">
         <f>IF(G7="","",COUNT($G$5:G7))</f>
@@ -8858,8 +9047,8 @@
         <v/>
       </c>
       <c r="M8" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G8="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N8" s="7">
         <f>IF(G8="","",COUNT($G$5:G8))</f>
@@ -8928,8 +9117,8 @@
         <v/>
       </c>
       <c r="M9" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G9="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N9" s="7">
         <f>IF(G9="","",COUNT($G$5:G9))</f>
@@ -8998,8 +9187,8 @@
         <v/>
       </c>
       <c r="M10" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G10="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N10" s="7">
         <f>IF(G10="","",COUNT($G$5:G10))</f>
@@ -9068,8 +9257,8 @@
         <v/>
       </c>
       <c r="M11" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G11="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N11" s="7">
         <f>IF(G11="","",COUNT($G$5:G11))</f>
@@ -9138,8 +9327,8 @@
         <v/>
       </c>
       <c r="M12" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G12="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N12" s="7">
         <f>IF(G12="","",COUNT($G$5:G12))</f>
@@ -9208,8 +9397,8 @@
         <v/>
       </c>
       <c r="M13" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G13="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N13" s="7">
         <f>IF(G13="","",COUNT($G$5:G13))</f>
@@ -9278,8 +9467,8 @@
         <v/>
       </c>
       <c r="M14" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G14="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N14" s="7">
         <f>IF(G14="","",COUNT($G$5:G14))</f>
@@ -9348,8 +9537,8 @@
         <v/>
       </c>
       <c r="M15" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f>IF(G15="","","окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется")</f>
+        <v>окно скользящего среднего 12 мес. еще не накоплено, фаза цикла не определяется</v>
       </c>
       <c r="N15" s="7">
         <f>IF(G15="","",COUNT($G$5:G15))</f>
@@ -9418,7 +9607,7 @@
         <v>норма</v>
       </c>
       <c r="M16" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="M5:M36" si="4">IF(L16="","",IF(L16="ниже тренда","возможное ослабление интереса",IF(L16="выше тренда","возможная фаза повышенного интереса","без выраженного отклонения")))</f>
         <v>без выраженного отклонения</v>
       </c>
       <c r="N16" s="7">
@@ -10844,7 +11033,7 @@
         <v>45444</v>
       </c>
       <c r="B37" s="3">
-        <f t="shared" ref="B37:B68" si="5">IF(A37="","",MONTH(A37))</f>
+        <f t="shared" ref="B37:B64" si="5">IF(A37="","",MONTH(A37))</f>
         <v>6</v>
       </c>
       <c r="C37" s="3" t="str">
@@ -10860,7 +11049,7 @@
         <v>2085</v>
       </c>
       <c r="F37" s="5">
-        <f t="shared" ref="F37:F68" si="7">IF(E37="","",IF(MAX($E$5:$E$64)=0,"",E37/MAX($E$5:$E$64)*100))</f>
+        <f t="shared" ref="F37:F64" si="7">IF(E37="","",IF(MAX($E$5:$E$64)=0,"",E37/MAX($E$5:$E$64)*100))</f>
         <v>58.045657015590201</v>
       </c>
       <c r="G37" s="5">
@@ -10872,7 +11061,7 @@
         <v>62.880475129918345</v>
       </c>
       <c r="I37" s="5">
-        <f t="shared" ref="I37:I68" si="8">IF(OR(G37="",H37="",H37=0),"",G37/H37)</f>
+        <f t="shared" ref="I37:I64" si="8">IF(OR(G37="",H37="",H37=0),"",G37/H37)</f>
         <v>0.92311097992916169</v>
       </c>
       <c r="J37" s="5">
@@ -10888,7 +11077,7 @@
         <v>ниже тренда</v>
       </c>
       <c r="M37" s="3" t="str">
-        <f t="shared" ref="M37:M68" si="9">IF(L37="","",IF(L37="ниже тренда","возможное ослабление интереса",IF(L37="выше тренда","возможная фаза повышенного интереса","без выраженного отклонения")))</f>
+        <f t="shared" ref="M37:M64" si="9">IF(L37="","",IF(L37="ниже тренда","возможное ослабление интереса",IF(L37="выше тренда","возможная фаза повышенного интереса","без выраженного отклонения")))</f>
         <v>возможное ослабление интереса</v>
       </c>
       <c r="N37" s="7">
@@ -13840,7 +14029,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -13898,22 +14087,22 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -13941,7 +14130,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C4" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A4)/COUNTIFS(Расчет!$B$5:$B$64,A4,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -13985,7 +14174,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C5" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A5)/COUNTIFS(Расчет!$B$5:$B$64,A5,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14029,7 +14218,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C6" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A6)/COUNTIFS(Расчет!$B$5:$B$64,A6,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14073,7 +14262,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C7" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A7)/COUNTIFS(Расчет!$B$5:$B$64,A7,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14117,7 +14306,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C8" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A8)/COUNTIFS(Расчет!$B$5:$B$64,A8,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14161,7 +14350,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C9" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A9)/COUNTIFS(Расчет!$B$5:$B$64,A9,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14205,7 +14394,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C10" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A10)/COUNTIFS(Расчет!$B$5:$B$64,A10,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14249,7 +14438,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C11" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A11)/COUNTIFS(Расчет!$B$5:$B$64,A11,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14293,7 +14482,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C12" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A12)/COUNTIFS(Расчет!$B$5:$B$64,A12,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14337,7 +14526,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C13" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A13)/COUNTIFS(Расчет!$B$5:$B$64,A13,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14381,7 +14570,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C14" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A14)/COUNTIFS(Расчет!$B$5:$B$64,A14,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14425,7 +14614,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C15" s="5">
         <f>IFERROR(SUMIFS(Расчет!$I$5:$I$64,Расчет!$B$5:$B$64,A15)/COUNTIFS(Расчет!$B$5:$B$64,A15,Расчет!$I$5:$I$64,"&gt;0"),"")</f>
@@ -14522,10 +14711,10 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -14554,7 +14743,7 @@
     </row>
     <row r="19" spans="1:26" ht="39.4">
       <c r="A19" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B19" s="5">
         <f>MAX($D$4:$D$15)</f>
@@ -14587,7 +14776,7 @@
     </row>
     <row r="20" spans="1:26" ht="39.4">
       <c r="A20" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5">
         <f>MIN($D$4:$D$15)</f>
@@ -14620,7 +14809,7 @@
     </row>
     <row r="21" spans="1:26" ht="26.25">
       <c r="A21" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B21" s="5">
         <f>B19-B20</f>
@@ -14653,7 +14842,7 @@
     </row>
     <row r="22" spans="1:26" ht="39.4">
       <c r="A22" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B22" s="3" t="str">
         <f>IF(B21&gt;=Настройки!$B$7,"выраженная сезонность",IF(B21&gt;=Настройки!$B$8,"умеренная сезонность","слабая сезонность"))</f>
@@ -14686,7 +14875,7 @@
     </row>
     <row r="23" spans="1:26" ht="26.25">
       <c r="A23" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B23" s="3" t="str">
         <f>IFERROR(INDEX($B$4:$B$15,MATCH(B19,$D$4:$D$15,0)),"")</f>
@@ -14719,7 +14908,7 @@
     </row>
     <row r="24" spans="1:26" ht="26.25">
       <c r="A24" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B24" s="3" t="str">
         <f>IFERROR(INDEX($B$4:$B$15,MATCH(B20,$D$4:$D$15,0)),"")</f>
@@ -16902,7 +17091,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -16960,16 +17149,16 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -16996,17 +17185,17 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B4" s="3">
         <f>COUNT(Расчет!$G$5:$G$64)</f>
         <v>60</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -17033,17 +17222,17 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="3" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B5" s="5">
         <f>IF(B4&lt;12,"",SUMIFS(Расчет!$G$5:$G$64,Расчет!$N$5:$N$64,"&gt;=1",Расчет!$N$5:$N$64,"&lt;=12")/COUNTIFS(Расчет!$N$5:$N$64,"&gt;=1",Расчет!$N$5:$N$64,"&lt;=12"))</f>
         <v>51.82117668893838</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -17070,17 +17259,17 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="3" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B6" s="5">
         <f>IF(B4&lt;12,"",SUMIFS(Расчет!$G$5:$G$64,Расчет!$N$5:$N$64,"&gt;="&amp;B4-11,Расчет!$N$5:$N$64,"&lt;="&amp;B4)/COUNTIFS(Расчет!$N$5:$N$64,"&gt;="&amp;B4-11,Расчет!$N$5:$N$64,"&lt;="&amp;B4))</f>
         <v>58.05493689680771</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -17107,17 +17296,17 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B7" s="5">
         <f>IF(OR(B5="",B6=""),"",B6-B5)</f>
         <v>6.2337602078693308</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -17144,17 +17333,17 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B8" s="4">
         <f>IF(OR(B5="",B6=""),"",B7/B5)</f>
         <v>0.12029368312665069</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -17181,17 +17370,17 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B9" s="5">
         <f>IFERROR(SLOPE(Расчет!$G$5:$G$64,Расчет!$N$5:$N$64),"")</f>
         <v>9.6372043459238596E-2</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -17218,17 +17407,17 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="str">
         <f>IF(B8="","",IF(B8&gt;=Настройки!$B$10,"растущий тренд",IF(B8&lt;=Настройки!$B$9,"снижающийся тренд","стабильный тренд")))</f>
         <v>стабильный тренд</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -17255,17 +17444,17 @@
     </row>
     <row r="11" spans="1:26" ht="52.5">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B11" s="3" t="str">
         <f>IF(B10="","Недостаточно данных",IF(B10="растущий тренд","Интерес аудитории растет; бизнес-идея может быть дополнительно проверена на платежеспособный спрос.",IF(B10="снижающийся тренд","Интерес аудитории снижается; требуется осторожная проверка ниши, сегмента и каналов продвижения.","Интерес аудитории относительно стабилен; целесообразно изучить структуру спроса, конкурентов и целевые сегменты.")))</f>
         <v>Интерес аудитории относительно стабилен; целесообразно изучить структуру спроса, конкурентов и целевые сегменты.</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -19810,7 +19999,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -19840,7 +20029,7 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="12" t="s">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -19898,10 +20087,10 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -19930,7 +20119,7 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B5" s="8">
         <f>IFERROR(INDEX(Расчет!$A$5:$A$64,Оценка_тренда!$B$4),"")</f>
@@ -19963,7 +20152,7 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B6" s="9">
         <f>IFERROR(INDEX(Расчет!$K$5:$K$64,Оценка_тренда!$B$4),"")</f>
@@ -19996,7 +20185,7 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" s="9" t="str">
         <f>IFERROR(INDEX(Расчет!$L$5:$L$64,Оценка_тренда!$B$4),"")</f>
@@ -20029,7 +20218,7 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B8" s="9">
         <f>MIN(Расчет!$K$5:$K$64)</f>
@@ -20062,7 +20251,7 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B9" s="9">
         <f>MAX(Расчет!$K$5:$K$64)</f>
@@ -20095,7 +20284,7 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B10" s="9">
         <f>B9-B8</f>
@@ -20184,28 +20373,28 @@
     </row>
     <row r="13" spans="1:26" ht="26.25">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -20256,8 +20445,8 @@
         <v/>
       </c>
       <c r="H14" s="3" t="str">
-        <f t="shared" ref="H14:H45" si="0">IF(G14="","",IF(G14="ниже тренда","период осторожного планирования продаж и бюджета",IF(G14="выше тренда","период активизации продвижения и продаж","обычный режим анализа спроса")))</f>
-        <v/>
+        <f>IF(B14="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -20308,8 +20497,8 @@
         <v/>
       </c>
       <c r="H15" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B15="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -20360,8 +20549,8 @@
         <v/>
       </c>
       <c r="H16" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B16="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -20412,8 +20601,8 @@
         <v/>
       </c>
       <c r="H17" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B17="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -20464,8 +20653,8 @@
         <v/>
       </c>
       <c r="H18" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B18="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -20516,8 +20705,8 @@
         <v/>
       </c>
       <c r="H19" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B19="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -20568,8 +20757,8 @@
         <v/>
       </c>
       <c r="H20" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B20="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -20620,8 +20809,8 @@
         <v/>
       </c>
       <c r="H21" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B21="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -20672,8 +20861,8 @@
         <v/>
       </c>
       <c r="H22" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B22="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -20724,8 +20913,8 @@
         <v/>
       </c>
       <c r="H23" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B23="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -20776,8 +20965,8 @@
         <v/>
       </c>
       <c r="H24" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B24="","","окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца")</f>
+        <v>окно 12 мес. не накоплено, период входит в расчет сезонности после 12-го месяца</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -20828,7 +21017,7 @@
         <v>норма</v>
       </c>
       <c r="H25" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H14:H45" si="0">IF(G25="","",IF(G25="ниже тренда","период осторожного планирования продаж и бюджета",IF(G25="выше тренда","период активизации продвижения и продаж","обычный режим анализа спроса")))</f>
         <v>обычный режим анализа спроса</v>
       </c>
       <c r="I25" s="1"/>
@@ -21920,7 +22109,7 @@
         <v>ниже тренда</v>
       </c>
       <c r="H46" s="3" t="str">
-        <f t="shared" ref="H46:H77" si="1">IF(G46="","",IF(G46="ниже тренда","период осторожного планирования продаж и бюджета",IF(G46="выше тренда","период активизации продвижения и продаж","обычный режим анализа спроса")))</f>
+        <f t="shared" ref="H46:H73" si="1">IF(G46="","",IF(G46="ниже тренда","период осторожного планирования продаж и бюджета",IF(G46="выше тренда","период активизации продвижения и продаж","обычный режим анализа спроса")))</f>
         <v>период осторожного планирования продаж и бюджета</v>
       </c>
       <c r="I46" s="1"/>
@@ -24131,7 +24320,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -24189,28 +24378,28 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -24236,25 +24425,25 @@
         <v>46297</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -26989,7 +27178,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -27047,22 +27236,22 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -27087,22 +27276,22 @@
     </row>
     <row r="4" spans="1:26" ht="26.25">
       <c r="A4" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -27127,22 +27316,22 @@
     </row>
     <row r="5" spans="1:26" ht="26.25">
       <c r="A5" s="3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -27167,21 +27356,23 @@
     </row>
     <row r="6" spans="1:26" ht="26.25">
       <c r="A6" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>126</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>209</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -27205,21 +27396,23 @@
     </row>
     <row r="7" spans="1:26" ht="26.25">
       <c r="A7" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>131</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -27243,21 +27436,23 @@
     </row>
     <row r="8" spans="1:26" ht="26.25">
       <c r="A8" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>136</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -27281,22 +27476,22 @@
     </row>
     <row r="9" spans="1:26" ht="26.25">
       <c r="A9" s="3" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -29891,7 +30086,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -29949,16 +30144,16 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -29985,16 +30180,16 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B4" s="5">
         <v>0.5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -30021,16 +30216,16 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="3" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B5" s="5">
         <v>0.5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -30057,16 +30252,16 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="3" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B6" s="5">
         <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -30093,16 +30288,16 @@
     </row>
     <row r="7" spans="1:26" ht="26.25">
       <c r="A7" s="3" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B7" s="5">
         <v>0.3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -30129,16 +30324,16 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="3" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B8" s="5">
         <v>0.15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -30165,16 +30360,16 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="3" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B9" s="5">
         <v>-0.15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -30201,16 +30396,16 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="3" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B10" s="5">
         <v>0.15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -30237,16 +30432,16 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="3" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B11" s="5">
         <v>0.9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -30273,16 +30468,16 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="3" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B12" s="5">
         <v>1.1000000000000001</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
